--- a/Account.xlsx
+++ b/Account.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>2026-04-03 00:10:03</t>
+          <t>2026-04-03 01:07:16</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/Account.xlsx
+++ b/Account.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3560" yWindow="1980" windowWidth="21600" windowHeight="11390" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3580" yWindow="2540" windowWidth="21600" windowHeight="11390" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -476,12 +476,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>2026-04-03 01:07:16</t>
+          <t>2026-04-08 19:56:17</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>71,309</t>
+          <t>114.377</t>
         </is>
       </c>
     </row>
@@ -498,12 +498,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-03 00:11:43</t>
+          <t>2026-04-03 16:56:41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.132</t>
+          <t>70,676</t>
         </is>
       </c>
     </row>
@@ -520,12 +520,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-03 00:16:24</t>
+          <t>2026-04-03 17:03:59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>71.138</t>
+          <t>70,697</t>
         </is>
       </c>
     </row>
@@ -542,12 +542,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-03 00:22:15</t>
+          <t>2026-04-03 17:11:19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>70,773</t>
+          <t>70,332</t>
         </is>
       </c>
     </row>
@@ -564,12 +564,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-03 00:23:25</t>
+          <t>2026-04-03 17:18:45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>73,011</t>
+          <t>72,560</t>
         </is>
       </c>
     </row>
